--- a/operatorslogin_excels/Raju_Login_details.xlsx
+++ b/operatorslogin_excels/Raju_Login_details.xlsx
@@ -409,10 +409,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>raju@gmail.com</v>
+        <v>psktravelspnr@gmail.comm</v>
       </c>
       <c r="B2" t="str">
-        <v>4343434343</v>
+        <v>9894447953</v>
       </c>
     </row>
   </sheetData>
